--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MICHIGAN_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MICHIGAN_2021.xlsx
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C202">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C210">
@@ -6097,7 +6097,7 @@
         <v>51</v>
       </c>
       <c r="D319">
-        <v>0.009368111682586333</v>
+        <v>0.009368111682586331</v>
       </c>
     </row>
     <row r="320">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C579">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C593">
